--- a/artfynd/A 50773-2022 artfynd.xlsx
+++ b/artfynd/A 50773-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50773-2022 artfynd.xlsx
+++ b/artfynd/A 50773-2022 artfynd.xlsx
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121143237</v>
+        <v>121143236</v>
       </c>
       <c r="B8" t="n">
-        <v>4766</v>
+        <v>5169</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,21 +1359,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>470868</v>
+        <v>470861</v>
       </c>
       <c r="R8" t="n">
-        <v>6537537</v>
+        <v>6537538</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121143239</v>
+        <v>121143238</v>
       </c>
       <c r="B9" t="n">
-        <v>94844</v>
+        <v>94854</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>470904</v>
+        <v>470895</v>
       </c>
       <c r="R9" t="n">
-        <v>6537515</v>
+        <v>6537532</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121143238</v>
+        <v>121143239</v>
       </c>
       <c r="B10" t="n">
-        <v>94844</v>
+        <v>94854</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>470895</v>
+        <v>470904</v>
       </c>
       <c r="R10" t="n">
-        <v>6537532</v>
+        <v>6537515</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121143236</v>
+        <v>121143237</v>
       </c>
       <c r="B11" t="n">
-        <v>5169</v>
+        <v>4766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1698,21 +1698,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>470861</v>
+        <v>470868</v>
       </c>
       <c r="R11" t="n">
-        <v>6537538</v>
+        <v>6537537</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 50773-2022 artfynd.xlsx
+++ b/artfynd/A 50773-2022 artfynd.xlsx
@@ -1460,10 +1460,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121143238</v>
+        <v>121143237</v>
       </c>
       <c r="B9" t="n">
-        <v>94854</v>
+        <v>4766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,31 +1476,32 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>100299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1508,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>470895</v>
+        <v>470868</v>
       </c>
       <c r="R9" t="n">
-        <v>6537532</v>
+        <v>6537537</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,6 +1545,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1682,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121143237</v>
+        <v>121143238</v>
       </c>
       <c r="B11" t="n">
-        <v>4766</v>
+        <v>94854</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1698,32 +1704,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100299</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1731,10 +1736,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>470868</v>
+        <v>470895</v>
       </c>
       <c r="R11" t="n">
-        <v>6537537</v>
+        <v>6537532</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1767,11 +1772,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-10-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 50773-2022 artfynd.xlsx
+++ b/artfynd/A 50773-2022 artfynd.xlsx
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121143236</v>
+        <v>121143237</v>
       </c>
       <c r="B8" t="n">
-        <v>5169</v>
+        <v>4766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,21 +1359,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>470861</v>
+        <v>470868</v>
       </c>
       <c r="R8" t="n">
-        <v>6537538</v>
+        <v>6537537</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121143237</v>
+        <v>121143236</v>
       </c>
       <c r="B9" t="n">
-        <v>4766</v>
+        <v>5169</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,21 +1476,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>470868</v>
+        <v>470861</v>
       </c>
       <c r="R9" t="n">
-        <v>6537537</v>
+        <v>6537538</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121143239</v>
+        <v>121143238</v>
       </c>
       <c r="B10" t="n">
-        <v>94854</v>
+        <v>94866</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,10 +1625,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>470904</v>
+        <v>470895</v>
       </c>
       <c r="R10" t="n">
-        <v>6537515</v>
+        <v>6537532</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121143238</v>
+        <v>121143239</v>
       </c>
       <c r="B11" t="n">
-        <v>94854</v>
+        <v>94866</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>470895</v>
+        <v>470904</v>
       </c>
       <c r="R11" t="n">
-        <v>6537532</v>
+        <v>6537515</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 50773-2022 artfynd.xlsx
+++ b/artfynd/A 50773-2022 artfynd.xlsx
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121143237</v>
+        <v>121143239</v>
       </c>
       <c r="B8" t="n">
-        <v>4766</v>
+        <v>94867</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,32 +1359,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100299</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1392,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>470868</v>
+        <v>470904</v>
       </c>
       <c r="R8" t="n">
-        <v>6537537</v>
+        <v>6537515</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1428,11 +1427,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-10-04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121143236</v>
+        <v>121143237</v>
       </c>
       <c r="B9" t="n">
-        <v>5169</v>
+        <v>4766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,21 +1470,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>470861</v>
+        <v>470868</v>
       </c>
       <c r="R9" t="n">
-        <v>6537538</v>
+        <v>6537537</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,7 +1574,7 @@
         <v>121143238</v>
       </c>
       <c r="B10" t="n">
-        <v>94866</v>
+        <v>94867</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1688,10 +1682,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121143239</v>
+        <v>121143236</v>
       </c>
       <c r="B11" t="n">
-        <v>94866</v>
+        <v>5169</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,31 +1698,32 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1736,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>470904</v>
+        <v>470861</v>
       </c>
       <c r="R11" t="n">
-        <v>6537515</v>
+        <v>6537538</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1772,6 +1767,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 50773-2022 artfynd.xlsx
+++ b/artfynd/A 50773-2022 artfynd.xlsx
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121143239</v>
+        <v>121143238</v>
       </c>
       <c r="B8" t="n">
-        <v>94867</v>
+        <v>94870</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>470904</v>
+        <v>470895</v>
       </c>
       <c r="R8" t="n">
-        <v>6537515</v>
+        <v>6537532</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121143237</v>
+        <v>121143236</v>
       </c>
       <c r="B9" t="n">
-        <v>4766</v>
+        <v>5172</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,21 +1470,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1503,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>470868</v>
+        <v>470861</v>
       </c>
       <c r="R9" t="n">
-        <v>6537537</v>
+        <v>6537538</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121143238</v>
+        <v>121143239</v>
       </c>
       <c r="B10" t="n">
-        <v>94867</v>
+        <v>94870</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>470895</v>
+        <v>470904</v>
       </c>
       <c r="R10" t="n">
-        <v>6537532</v>
+        <v>6537515</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121143236</v>
+        <v>121143237</v>
       </c>
       <c r="B11" t="n">
-        <v>5169</v>
+        <v>4769</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1698,21 +1698,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>470861</v>
+        <v>470868</v>
       </c>
       <c r="R11" t="n">
-        <v>6537538</v>
+        <v>6537537</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 50773-2022 artfynd.xlsx
+++ b/artfynd/A 50773-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1797,6 +1797,708 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129207175</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Norra Välevattnet, Norra Välevattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>470709</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6537605</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack och barkfläkning med rinnande kåda på gran ca 5 m öster om vägen.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129207012</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Norra Välevattnet, Norra Välevattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>470730</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6537519</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack och barkfläkning med rinnande kåda på gran ca 25 m öster om vägen.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129206620</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Norra Välevattnet, Norra Välevattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>470714</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6537368</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt med färska ringhack med rinnande kåda på tall ca 10 meter öster om vägen.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129206880</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Norra Välevattnet, Norra Välevattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>470725</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6537519</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack  och barkfläkning med rinnande kåda på gran ca 20 m öster om vägen.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129206663</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57717</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Norra Välevattnet, Norra Välevattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>470833</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6537406</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Kly, kly, kly.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129207213</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Norra Välevattnet, Norra Välevattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>470713</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6537602</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Riktigt färska ringhack och barkfläkning med på gran ca 20 m öster om vägen.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50773-2022 artfynd.xlsx
+++ b/artfynd/A 50773-2022 artfynd.xlsx
@@ -2267,38 +2267,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129206663</v>
+        <v>129207213</v>
       </c>
       <c r="B16" t="n">
-        <v>57717</v>
+        <v>57723</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102977</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470833</v>
+        <v>470713</v>
       </c>
       <c r="R16" t="n">
-        <v>6537406</v>
+        <v>6537602</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Kly, kly, kly.</t>
+          <t>Riktigt färska ringhack och barkfläkning med på gran ca 20 m öster om vägen.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2384,38 +2384,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129207213</v>
+        <v>129206663</v>
       </c>
       <c r="B17" t="n">
-        <v>57723</v>
+        <v>57717</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>102977</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2424,10 +2424,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470713</v>
+        <v>470833</v>
       </c>
       <c r="R17" t="n">
-        <v>6537602</v>
+        <v>6537406</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Riktigt färska ringhack och barkfläkning med på gran ca 20 m öster om vägen.</t>
+          <t>Kly, kly, kly.</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 50773-2022 artfynd.xlsx
+++ b/artfynd/A 50773-2022 artfynd.xlsx
@@ -1802,7 +1802,7 @@
         <v>129207175</v>
       </c>
       <c r="B12" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>129207012</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>129206620</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>129206880</v>
       </c>
       <c r="B15" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>129207213</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>129206663</v>
       </c>
       <c r="B17" t="n">
-        <v>57717</v>
+        <v>57719</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 50773-2022 artfynd.xlsx
+++ b/artfynd/A 50773-2022 artfynd.xlsx
@@ -1802,7 +1802,7 @@
         <v>129207175</v>
       </c>
       <c r="B12" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>129207012</v>
       </c>
       <c r="B13" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>129206620</v>
       </c>
       <c r="B14" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>129206880</v>
       </c>
       <c r="B15" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>129207213</v>
       </c>
       <c r="B16" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>129206663</v>
       </c>
       <c r="B17" t="n">
-        <v>57719</v>
+        <v>57721</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 50773-2022 artfynd.xlsx
+++ b/artfynd/A 50773-2022 artfynd.xlsx
@@ -2267,38 +2267,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129207213</v>
+        <v>129206663</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>57721</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>102977</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470713</v>
+        <v>470833</v>
       </c>
       <c r="R16" t="n">
-        <v>6537602</v>
+        <v>6537406</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Riktigt färska ringhack och barkfläkning med på gran ca 20 m öster om vägen.</t>
+          <t>Kly, kly, kly.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2384,38 +2384,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129206663</v>
+        <v>129207213</v>
       </c>
       <c r="B17" t="n">
-        <v>57721</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102977</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2424,10 +2424,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470833</v>
+        <v>470713</v>
       </c>
       <c r="R17" t="n">
-        <v>6537406</v>
+        <v>6537602</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Kly, kly, kly.</t>
+          <t>Riktigt färska ringhack och barkfläkning med på gran ca 20 m öster om vägen.</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 50773-2022 artfynd.xlsx
+++ b/artfynd/A 50773-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2267,38 +2267,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129206663</v>
+        <v>129207213</v>
       </c>
       <c r="B16" t="n">
-        <v>57721</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102977</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470833</v>
+        <v>470713</v>
       </c>
       <c r="R16" t="n">
-        <v>6537406</v>
+        <v>6537602</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Kly, kly, kly.</t>
+          <t>Riktigt färska ringhack och barkfläkning med på gran ca 20 m öster om vägen.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2384,38 +2384,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129207213</v>
+        <v>129206663</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>57721</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>102977</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2424,10 +2424,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470713</v>
+        <v>470833</v>
       </c>
       <c r="R17" t="n">
-        <v>6537602</v>
+        <v>6537406</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Riktigt färska ringhack och barkfläkning med på gran ca 20 m öster om vägen.</t>
+          <t>Kly, kly, kly.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2498,6 +2498,123 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129379827</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Norra Välevattnet, Norra Välevattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>470865</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6537633</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Förekomst spridd över perioden</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50773-2022 artfynd.xlsx
+++ b/artfynd/A 50773-2022 artfynd.xlsx
@@ -2267,38 +2267,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129206663</v>
+        <v>129207213</v>
       </c>
       <c r="B16" t="n">
-        <v>57721</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102977</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470833</v>
+        <v>470713</v>
       </c>
       <c r="R16" t="n">
-        <v>6537406</v>
+        <v>6537602</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Kly, kly, kly.</t>
+          <t>Riktigt färska ringhack och barkfläkning med på gran ca 20 m öster om vägen.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2384,38 +2384,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129207213</v>
+        <v>129206663</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>57721</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>102977</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2424,10 +2424,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470713</v>
+        <v>470833</v>
       </c>
       <c r="R17" t="n">
-        <v>6537602</v>
+        <v>6537406</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Riktigt färska ringhack och barkfläkning med på gran ca 20 m öster om vägen.</t>
+          <t>Kly, kly, kly.</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 50773-2022 artfynd.xlsx
+++ b/artfynd/A 50773-2022 artfynd.xlsx
@@ -2033,7 +2033,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129206620</v>
+        <v>129206880</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470714</v>
+        <v>470725</v>
       </c>
       <c r="R14" t="n">
-        <v>6537368</v>
+        <v>6537519</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack med rinnande kåda på tall ca 10 meter öster om vägen.</t>
+          <t>Ringhack  och barkfläkning med rinnande kåda på gran ca 20 m öster om vägen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2150,7 +2150,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129206880</v>
+        <v>129206620</v>
       </c>
       <c r="B15" t="n">
         <v>57727</v>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>470725</v>
+        <v>470714</v>
       </c>
       <c r="R15" t="n">
-        <v>6537519</v>
+        <v>6537368</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2235,12 +2235,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack  och barkfläkning med rinnande kåda på gran ca 20 m öster om vägen.</t>
+          <t>Rikligt med färska ringhack med rinnande kåda på tall ca 10 meter öster om vägen.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2267,38 +2267,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129207213</v>
+        <v>129206663</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>57721</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>102977</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470713</v>
+        <v>470833</v>
       </c>
       <c r="R16" t="n">
-        <v>6537602</v>
+        <v>6537406</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Riktigt färska ringhack och barkfläkning med på gran ca 20 m öster om vägen.</t>
+          <t>Kly, kly, kly.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2384,38 +2384,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129206663</v>
+        <v>129207213</v>
       </c>
       <c r="B17" t="n">
-        <v>57721</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102977</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2424,10 +2424,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470833</v>
+        <v>470713</v>
       </c>
       <c r="R17" t="n">
-        <v>6537406</v>
+        <v>6537602</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Kly, kly, kly.</t>
+          <t>Riktigt färska ringhack och barkfläkning med på gran ca 20 m öster om vägen.</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 50773-2022 artfynd.xlsx
+++ b/artfynd/A 50773-2022 artfynd.xlsx
@@ -2033,7 +2033,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129206880</v>
+        <v>129206620</v>
       </c>
       <c r="B14" t="n">
         <v>57727</v>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470725</v>
+        <v>470714</v>
       </c>
       <c r="R14" t="n">
-        <v>6537519</v>
+        <v>6537368</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack  och barkfläkning med rinnande kåda på gran ca 20 m öster om vägen.</t>
+          <t>Rikligt med färska ringhack med rinnande kåda på tall ca 10 meter öster om vägen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2150,7 +2150,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129206620</v>
+        <v>129206880</v>
       </c>
       <c r="B15" t="n">
         <v>57727</v>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>470714</v>
+        <v>470725</v>
       </c>
       <c r="R15" t="n">
-        <v>6537368</v>
+        <v>6537519</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2235,12 +2235,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack med rinnande kåda på tall ca 10 meter öster om vägen.</t>
+          <t>Ringhack  och barkfläkning med rinnande kåda på gran ca 20 m öster om vägen.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2267,38 +2267,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129206663</v>
+        <v>129207213</v>
       </c>
       <c r="B16" t="n">
-        <v>57721</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102977</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470833</v>
+        <v>470713</v>
       </c>
       <c r="R16" t="n">
-        <v>6537406</v>
+        <v>6537602</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Kly, kly, kly.</t>
+          <t>Riktigt färska ringhack och barkfläkning med på gran ca 20 m öster om vägen.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2384,38 +2384,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129207213</v>
+        <v>129206663</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>57721</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>102977</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2424,10 +2424,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470713</v>
+        <v>470833</v>
       </c>
       <c r="R17" t="n">
-        <v>6537602</v>
+        <v>6537406</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Riktigt färska ringhack och barkfläkning med på gran ca 20 m öster om vägen.</t>
+          <t>Kly, kly, kly.</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 50773-2022 artfynd.xlsx
+++ b/artfynd/A 50773-2022 artfynd.xlsx
@@ -1802,7 +1802,7 @@
         <v>129207175</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>129207012</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>129206620</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>129206880</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2267,38 +2267,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129206663</v>
+        <v>129207213</v>
       </c>
       <c r="B16" t="n">
-        <v>57721</v>
+        <v>57730</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102977</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2307,10 +2307,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470833</v>
+        <v>470713</v>
       </c>
       <c r="R16" t="n">
-        <v>6537406</v>
+        <v>6537602</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Kly, kly, kly.</t>
+          <t>Riktigt färska ringhack och barkfläkning med på gran ca 20 m öster om vägen.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2384,38 +2384,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129207213</v>
+        <v>129206663</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>102977</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2424,10 +2424,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470713</v>
+        <v>470833</v>
       </c>
       <c r="R17" t="n">
-        <v>6537602</v>
+        <v>6537406</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Riktigt färska ringhack och barkfläkning med på gran ca 20 m öster om vägen.</t>
+          <t>Kly, kly, kly.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,7 +2504,7 @@
         <v>129379827</v>
       </c>
       <c r="B18" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 50773-2022 artfynd.xlsx
+++ b/artfynd/A 50773-2022 artfynd.xlsx
@@ -2504,7 +2504,7 @@
         <v>129379827</v>
       </c>
       <c r="B18" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 50773-2022 artfynd.xlsx
+++ b/artfynd/A 50773-2022 artfynd.xlsx
@@ -2504,7 +2504,7 @@
         <v>129379827</v>
       </c>
       <c r="B18" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 50773-2022 artfynd.xlsx
+++ b/artfynd/A 50773-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113140114</v>
+        <v>113140154</v>
       </c>
       <c r="B2" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>1036</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Hållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Menegazzia terebrata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>470865</v>
+        <v>470876</v>
       </c>
       <c r="R2" t="n">
-        <v>6537532</v>
+        <v>6537531</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,6 +753,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>på klibbal</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,57 +785,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113140154</v>
+        <v>121143238</v>
       </c>
       <c r="B3" t="n">
-        <v>78626</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1036</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hållav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Menegazzia terebrata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norra Välevattnet, Vg</t>
+          <t>Hallsberg-Laxå, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>470876</v>
+        <v>470895</v>
       </c>
       <c r="R3" t="n">
-        <v>6537531</v>
+        <v>6537532</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,17 +858,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>på klibbal</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,15 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113140164</v>
+        <v>121143239</v>
       </c>
       <c r="B4" t="n">
-        <v>74459</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,41 +902,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norra Välevattnet, Vg</t>
+          <t>Hallsberg-Laxå, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>470864</v>
+        <v>470904</v>
       </c>
       <c r="R4" t="n">
-        <v>6537550</v>
+        <v>6537515</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,12 +964,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,46 +997,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113140429</v>
+        <v>113140142</v>
       </c>
       <c r="B5" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>2590</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471004</v>
+        <v>470871</v>
       </c>
       <c r="R5" t="n">
-        <v>6537474</v>
+        <v>6537535</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,43 +1103,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113140413</v>
+        <v>113140429</v>
       </c>
       <c r="B6" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1169,10 +1145,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471061</v>
+        <v>471004</v>
       </c>
       <c r="R6" t="n">
-        <v>6537493</v>
+        <v>6537474</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,47 +1208,41 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113140142</v>
+        <v>113140413</v>
       </c>
       <c r="B7" t="n">
-        <v>95242</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1280,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>470871</v>
+        <v>471061</v>
       </c>
       <c r="R7" t="n">
-        <v>6537535</v>
+        <v>6537493</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,15 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121143238</v>
+        <v>113140164</v>
       </c>
       <c r="B8" t="n">
-        <v>94870</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,42 +1324,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>6428</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hallsberg-Laxå, Vg</t>
+          <t>Norra Välevattnet, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>470895</v>
+        <v>470864</v>
       </c>
       <c r="R8" t="n">
-        <v>6537532</v>
+        <v>6537550</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,12 +1385,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,15 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121143236</v>
+        <v>121143412</v>
       </c>
       <c r="B9" t="n">
-        <v>5172</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,32 +1429,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1503,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>470861</v>
+        <v>470878</v>
       </c>
       <c r="R9" t="n">
-        <v>6537538</v>
+        <v>6537485</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,17 +1491,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1552,7 +1505,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1571,61 +1523,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121143239</v>
+        <v>129206620</v>
       </c>
       <c r="B10" t="n">
-        <v>94870</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hallsberg-Laxå, Vg</t>
+          <t>Norra Välevattnet, Norra Välevattnet, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>470904</v>
+        <v>470714</v>
       </c>
       <c r="R10" t="n">
-        <v>6537515</v>
+        <v>6537368</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1649,12 +1593,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt med färska ringhack med rinnande kåda på tall ca 10 meter öster om vägen.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,81 +1622,71 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121143237</v>
+        <v>129206880</v>
       </c>
       <c r="B11" t="n">
-        <v>4769</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100299</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hallsberg-Laxå, Vg</t>
+          <t>Norra Välevattnet, Norra Välevattnet, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>470868</v>
+        <v>470725</v>
       </c>
       <c r="R11" t="n">
-        <v>6537537</v>
+        <v>6537519</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1761,17 +1710,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>kläckhål och/eller gnag</t>
+          <t>Ringhack  och barkfläkning med rinnande kåda på gran ca 20 m öster om vägen.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,29 +1739,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129207175</v>
+        <v>129207012</v>
       </c>
       <c r="B12" t="n">
-        <v>57730</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1839,10 +1797,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>470709</v>
+        <v>470730</v>
       </c>
       <c r="R12" t="n">
-        <v>6537605</v>
+        <v>6537519</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1874,7 +1832,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1884,12 +1842,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack och barkfläkning med rinnande kåda på gran ca 5 m öster om vägen.</t>
+          <t>Ringhack och barkfläkning med rinnande kåda på gran ca 25 m öster om vägen.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1916,10 +1874,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129207012</v>
+        <v>129207175</v>
       </c>
       <c r="B13" t="n">
-        <v>57730</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,10 +1914,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>470730</v>
+        <v>470709</v>
       </c>
       <c r="R13" t="n">
-        <v>6537519</v>
+        <v>6537605</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1991,7 +1949,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,12 +1959,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack och barkfläkning med rinnande kåda på gran ca 25 m öster om vägen.</t>
+          <t>Ringhack och barkfläkning med rinnande kåda på gran ca 5 m öster om vägen.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2033,10 +1991,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129206620</v>
+        <v>129207213</v>
       </c>
       <c r="B14" t="n">
-        <v>57730</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2073,10 +2031,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>470714</v>
+        <v>470713</v>
       </c>
       <c r="R14" t="n">
-        <v>6537368</v>
+        <v>6537602</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2108,7 +2066,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2118,12 +2076,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack med rinnande kåda på tall ca 10 meter öster om vägen.</t>
+          <t>Riktigt färska ringhack och barkfläkning med på gran ca 20 m öster om vägen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2150,53 +2108,56 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129206880</v>
+        <v>121143243</v>
       </c>
       <c r="B15" t="n">
-        <v>57730</v>
+        <v>57141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Norra Välevattnet, Norra Välevattnet, Vg</t>
+          <t>Hallsberg-Laxå, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>470725</v>
+        <v>470898</v>
       </c>
       <c r="R15" t="n">
-        <v>6537519</v>
+        <v>6537474</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2220,27 +2181,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack  och barkfläkning med rinnande kåda på gran ca 20 m öster om vägen.</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2255,65 +2201,69 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129207213</v>
+        <v>113140127</v>
       </c>
       <c r="B16" t="n">
-        <v>57730</v>
+        <v>4775</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norra Välevattnet, Norra Välevattnet, Vg</t>
+          <t>Norra Välevattnet, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470713</v>
+        <v>470876</v>
       </c>
       <c r="R16" t="n">
-        <v>6537602</v>
+        <v>6537522</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2337,27 +2287,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:46</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Riktigt färska ringhack och barkfläkning med på gran ca 20 m öster om vägen.</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2366,28 +2301,29 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129206663</v>
+        <v>121143237</v>
       </c>
       <c r="B17" t="n">
-        <v>57724</v>
+        <v>4775</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,42 +2331,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102977</v>
+        <v>100299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norra Välevattnet, Norra Välevattnet, Vg</t>
+          <t>Hallsberg-Laxå, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470833</v>
+        <v>470868</v>
       </c>
       <c r="R17" t="n">
-        <v>6537406</v>
+        <v>6537537</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2454,27 +2394,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Kly, kly, kly.</t>
+          <t>kläckhål och/eller gnag</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2483,71 +2413,76 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129379827</v>
+        <v>113140114</v>
       </c>
       <c r="B18" t="n">
-        <v>57896</v>
+        <v>5179</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norra Välevattnet, Norra Välevattnet, Vg</t>
+          <t>Norra Välevattnet, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
         <v>470865</v>
       </c>
       <c r="R18" t="n">
-        <v>6537633</v>
+        <v>6537532</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2571,27 +2506,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>07:15</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Förekomst spridd över perioden</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2600,21 +2520,1857 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>113140122</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Norra Välevattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>470876</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6537522</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>113140175</v>
+      </c>
+      <c r="B20" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Norra Välevattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>470900</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6537473</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>113140184</v>
+      </c>
+      <c r="B21" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Norra Välevattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>470907</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6537473</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>113140220</v>
+      </c>
+      <c r="B22" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Norra Välevattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>470913</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6537469</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>113140273</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Norra Välevattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>471045</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6537610</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121143236</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hallsberg-Laxå, Vg</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>470861</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6537538</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129206663</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Norra Välevattnet, Norra Välevattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>470833</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6537406</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Kly, kly, kly.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129379827</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Norra Välevattnet, Norra Välevattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>470865</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6537633</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Förekomst spridd över perioden</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
           <t>David Tverling</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
+      <c r="AX26" t="inlineStr">
         <is>
           <t>David Tverling</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>113140126</v>
+      </c>
+      <c r="B27" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Norra Välevattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>470876</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6537522</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>113140282</v>
+      </c>
+      <c r="B28" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Norra Välevattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>471040</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6537607</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>113140109</v>
+      </c>
+      <c r="B29" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Norra Välevattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>470867</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6537516</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>113140275</v>
+      </c>
+      <c r="B30" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Norra Välevattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>471045</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6537610</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>121143244</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hallsberg-Laxå, Vg</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>470861</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6537510</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>121143245</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hallsberg-Laxå, Vg</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>470904</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6537459</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>121143246</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hallsberg-Laxå, Vg</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>470909</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6537452</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>121143247</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hallsberg-Laxå, Vg</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>470916</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6537438</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>113140265</v>
+      </c>
+      <c r="B35" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Norra Välevattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>471036</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6537541</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50773-2022 artfynd.xlsx
+++ b/artfynd/A 50773-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113140154</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121143238</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121143239</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113140142</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1205,6 +1230,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113140429</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1310,6 +1340,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113140413</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1415,6 +1450,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113140164</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121143412</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1637,6 +1682,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129206620</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1754,6 +1804,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129206880</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1871,6 +1926,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129207012</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1988,6 +2048,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129207175</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2105,6 +2170,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129207213</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2210,6 +2280,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121143243</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2317,6 +2392,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113140127</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2429,6 +2509,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121143237</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2536,6 +2621,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113140114</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2643,6 +2733,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113140122</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2750,6 +2845,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113140175</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2857,6 +2957,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113140184</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2964,6 +3069,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113140220</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3071,6 +3181,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113140273</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3183,6 +3298,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121143236</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3300,6 +3420,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129206663</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3417,6 +3542,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129379827</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3524,6 +3654,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113140126</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3631,6 +3766,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113140282</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3738,6 +3878,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113140109</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3845,6 +3990,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113140275</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3950,6 +4100,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121143244</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4055,6 +4210,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121143245</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4160,6 +4320,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121143246</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4265,6 +4430,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121143247</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4371,8 +4541,49 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113140265</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>